--- a/public/exports-from-60/11259979.xlsx
+++ b/public/exports-from-60/11259979.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60/11259979.xlsx
+++ b/public/exports-from-60/11259979.xlsx
@@ -2666,17 +2666,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beringsvej 8</t>
+          <t xml:space="preserve">Frederiksberg Alle 48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1820</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030255</t>
+          <t xml:space="preserve">100025821</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>413</v>
+        <v>996</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218022</t>
+          <t xml:space="preserve">311217955</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2736,35 +2736,35 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Alle 48</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025821</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J37">
-        <v>996</v>
+        <v>132</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217955</t>
+          <t xml:space="preserve">311223472</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2811,35 +2811,35 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Orla Lehmanns Vej 5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">100029573</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223472</t>
+          <t xml:space="preserve">311223812</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-19</t>
+          <t xml:space="preserve">2027-01-21</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orla Lehmanns Vej 5</t>
+          <t xml:space="preserve">Segelckesvej 7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029573</t>
+          <t xml:space="preserve">100030239</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>238</v>
+        <v>408</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223812</t>
+          <t xml:space="preserve">311223800</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2981,11 +2981,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J40">
-        <v>408</v>
+        <v>197</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segelckesvej 7</t>
+          <t xml:space="preserve">Thorvaldsensvej 24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030239</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>197</v>
+        <v>3792</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223800</t>
+          <t xml:space="preserve">311223802</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 24</t>
+          <t xml:space="preserve">Storm Petersens Vej 5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100047575</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="J42">
-        <v>3792</v>
+        <v>297</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223802</t>
+          <t xml:space="preserve">311225730</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-21</t>
+          <t xml:space="preserve">2027-01-31</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 5</t>
+          <t xml:space="preserve">Hortensiavej 11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047575</t>
+          <t xml:space="preserve">100025624</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>297</v>
+        <v>440</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225730</t>
+          <t xml:space="preserve">311226748</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-31</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 11</t>
+          <t xml:space="preserve">Hortensiavej 13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025624</t>
+          <t xml:space="preserve">100025599</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>440</v>
+        <v>255</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226748</t>
+          <t xml:space="preserve">311226749</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">230</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 13</t>
+          <t xml:space="preserve">Biskop Svanes Vej 75</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">3460</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025599</t>
+          <t xml:space="preserve">8312706</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="J45">
-        <v>255</v>
+        <v>1322</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226749</t>
+          <t xml:space="preserve">311231330</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">230</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Svanes Vej 75</t>
+          <t xml:space="preserve">Nørrevænget 14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3460</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8312706</t>
+          <t xml:space="preserve">2137707</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>1322</v>
+        <v>295</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231330</t>
+          <t xml:space="preserve">311227340</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3486,22 +3486,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 14</t>
+          <t xml:space="preserve">Amicisvej 9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137707</t>
+          <t xml:space="preserve">100025655</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="J47">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227340</t>
+          <t xml:space="preserve">311227832</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 9</t>
+          <t xml:space="preserve">Bülowsvej 14A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025655</t>
+          <t xml:space="preserve">100026669</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="J48">
-        <v>340</v>
+        <v>626</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227832</t>
+          <t xml:space="preserve">311227831</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 14A</t>
+          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026669</t>
+          <t xml:space="preserve">100025685</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>626</v>
+        <v>953</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227831</t>
+          <t xml:space="preserve">311229051</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
+          <t xml:space="preserve">Frydendalsvej 19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025685</t>
+          <t xml:space="preserve">100028929</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,11 +3735,11 @@
         </is>
       </c>
       <c r="J50">
-        <v>953</v>
+        <v>805</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229051</t>
+          <t xml:space="preserve">311229048</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 19</t>
+          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028929</t>
+          <t xml:space="preserve">100027090</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,21 +3810,21 @@
         </is>
       </c>
       <c r="J51">
-        <v>805</v>
+        <v>589</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229048</t>
+          <t xml:space="preserve">311230550</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,30 +3866,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
+          <t xml:space="preserve">Junggreensvej 12B</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027090</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J52">
-        <v>589</v>
+        <v>1152</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230550</t>
+          <t xml:space="preserve">311230598</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3941,30 +3941,30 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junggreensvej 12B</t>
+          <t xml:space="preserve">N.J. Fjords Alle 15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100026522</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53">
-        <v>1152</v>
+        <v>300</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230598</t>
+          <t xml:space="preserve">311230618</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 15</t>
+          <t xml:space="preserve">N.J. Fjords Alle 17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J54">
-        <v>300</v>
+        <v>376</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,30 +4091,30 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 17</t>
+          <t xml:space="preserve">Niels Ebbesens Vej 21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026522</t>
+          <t xml:space="preserve">100027029</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>376</v>
+        <v>190</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230618</t>
+          <t xml:space="preserve">311230611</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,17 +4166,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Ebbesens Vej 21</t>
+          <t xml:space="preserve">Nyelandsvej 66</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027029</t>
+          <t xml:space="preserve">100029714</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>190</v>
+        <v>342</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230611</t>
+          <t xml:space="preserve">311230609</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 75</t>
+          <t xml:space="preserve">Sankt Knuds Vej 7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029720</t>
+          <t xml:space="preserve">100026917</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>1334</v>
+        <v>433</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230619</t>
+          <t xml:space="preserve">311230540</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 66</t>
+          <t xml:space="preserve">Bakkegårds Alle 18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1804</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029714</t>
+          <t xml:space="preserve">191034</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>342</v>
+        <v>1225</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230609</t>
+          <t xml:space="preserve">311230651</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 7</t>
+          <t xml:space="preserve">Dronning Olgas Vej 6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026917</t>
+          <t xml:space="preserve">100028120</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>433</v>
+        <v>580</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230540</t>
+          <t xml:space="preserve">311230652</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,30 +4466,30 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkegårds Alle 18</t>
+          <t xml:space="preserve">Dronning Olgas Vej 6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">191034</t>
+          <t xml:space="preserve">100028120</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>1225</v>
+        <v>72</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230651</t>
+          <t xml:space="preserve">311230652</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Olgas Vej 6</t>
+          <t xml:space="preserve">Rahbeks Alle 19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1801</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028120</t>
+          <t xml:space="preserve">100028743</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>580</v>
+        <v>388</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230652</t>
+          <t xml:space="preserve">311231234</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Olgas Vej 6</t>
+          <t xml:space="preserve">La Cours Vej 2A</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028120</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230652</t>
+          <t xml:space="preserve">311231520</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 40</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029487</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>1071</v>
+        <v>1209</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231229</t>
+          <t xml:space="preserve">311231683</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4761,35 +4761,35 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbeks Alle 19</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028743</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J64">
-        <v>388</v>
+        <v>144</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231234</t>
+          <t xml:space="preserve">311231683</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,30 +4841,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Cours Vej 2A</t>
+          <t xml:space="preserve">Thorvaldsensvej 26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J65">
-        <v>150</v>
+        <v>422</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231520</t>
+          <t xml:space="preserve">311233222</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-01</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Oddenvej 90B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">2428914</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>1209</v>
+        <v>398</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231683</t>
+          <t xml:space="preserve">311233782</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4986,35 +4986,35 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Skellet 27A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J67">
-        <v>144</v>
+        <v>476</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231683</t>
+          <t xml:space="preserve">311233769</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,30 +5066,30 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 26</t>
+          <t xml:space="preserve">Skellet 27A</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J68">
-        <v>422</v>
+        <v>224</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233222</t>
+          <t xml:space="preserve">311233769</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5136,35 +5136,35 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oddenvej 90B</t>
+          <t xml:space="preserve">Vodroffsvej 44</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428914</t>
+          <t xml:space="preserve">100027252</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J69">
-        <v>398</v>
+        <v>178</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233782</t>
+          <t xml:space="preserve">311234441</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,30 +5216,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27A</t>
+          <t xml:space="preserve">Vodroffsvej 46</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100027252</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>476</v>
+        <v>1486</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233769</t>
+          <t xml:space="preserve">311234441</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27A</t>
+          <t xml:space="preserve">Allegade 31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100025702</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>224</v>
+        <v>29942</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233769</t>
+          <t xml:space="preserve">311234962</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,30 +5366,30 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vodroffsvej 44</t>
+          <t xml:space="preserve">Skellet 27C</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027252</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J72">
-        <v>178</v>
+        <v>1915</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234441</t>
+          <t xml:space="preserve">311236260</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vodroffsvej 46</t>
+          <t xml:space="preserve">Edisonsvej 3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027252</t>
+          <t xml:space="preserve">100025577</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>1486</v>
+        <v>228</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234441</t>
+          <t xml:space="preserve">311247695</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 31</t>
+          <t xml:space="preserve">Edisonsvej 3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025702</t>
+          <t xml:space="preserve">100025577</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J74">
-        <v>29942</v>
+        <v>525</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234962</t>
+          <t xml:space="preserve">311247695</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosegårdsvej 10</t>
+          <t xml:space="preserve">Ingemannsvej 21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1967</t>
+          <t xml:space="preserve">1964</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026430</t>
+          <t xml:space="preserve">100026391</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>446</v>
+        <v>1000</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235357</t>
+          <t xml:space="preserve">311248626</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27C</t>
+          <t xml:space="preserve">Søndre Fasanvej 40</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100028380</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="J76">
-        <v>1915</v>
+        <v>1699</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236260</t>
+          <t xml:space="preserve">311248632</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 3</t>
+          <t xml:space="preserve">Bülowsvej 20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025577</t>
+          <t xml:space="preserve">100026777</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>228</v>
+        <v>454</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247695</t>
+          <t xml:space="preserve">311248790</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 3</t>
+          <t xml:space="preserve">Storm Petersens Vej 4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025577</t>
+          <t xml:space="preserve">100047577</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>525</v>
+        <v>2679</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247695</t>
+          <t xml:space="preserve">311256544</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,40 +5891,40 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingemannsvej 21</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1964</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026391</t>
+          <t xml:space="preserve">100030861, 100227750, 100227751</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J79">
-        <v>1000</v>
+        <v>6331</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248626</t>
+          <t xml:space="preserve">311268443</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-08-24</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Fasanvej 40</t>
+          <t xml:space="preserve">Mariendalsvej 21A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028380</t>
+          <t xml:space="preserve">100028065</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,21 +5985,21 @@
         </is>
       </c>
       <c r="J80">
-        <v>1699</v>
+        <v>1008</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248632</t>
+          <t xml:space="preserve">311269303</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 20</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026777</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,21 +6060,21 @@
         </is>
       </c>
       <c r="J81">
-        <v>454</v>
+        <v>825</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248790</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,40 +6116,40 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 4</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047577</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>2679</v>
+        <v>439</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256544</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,40 +6191,40 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861, 100227750, 100227751</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J83">
-        <v>6331</v>
+        <v>464</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268443</t>
+          <t xml:space="preserve">311285951</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-24</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,40 +6266,40 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariendalsvej 21A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028065</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J84">
-        <v>1008</v>
+        <v>371</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269303</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-29</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Dirch Passers Allé 8A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029781</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,21 +6360,21 @@
         </is>
       </c>
       <c r="J85">
-        <v>825</v>
+        <v>3880</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311293188</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,40 +6416,40 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Helgesvej 29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100026188</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>439</v>
+        <v>6682</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311373826</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-04-30</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,40 +6491,40 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J87">
-        <v>464</v>
+        <v>386</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285951</t>
+          <t xml:space="preserve">311379731</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,40 +6566,40 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J88">
-        <v>371</v>
+        <v>443</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311379734</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirch Passers Allé 8A</t>
+          <t xml:space="preserve">Nyelandsvej 70</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029781</t>
+          <t xml:space="preserve">100029712</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,21 +6660,21 @@
         </is>
       </c>
       <c r="J89">
-        <v>3880</v>
+        <v>311</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293188</t>
+          <t xml:space="preserve">311379735</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 29</t>
+          <t xml:space="preserve">Nyelandsvej 70</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026188</t>
+          <t xml:space="preserve">100029712</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J90">
-        <v>6682</v>
+        <v>126</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373826</t>
+          <t xml:space="preserve">311379735</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-30</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Nyelandsvej 72</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100029711</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>386</v>
+        <v>542</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379731</t>
+          <t xml:space="preserve">311379737</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100028525</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>443</v>
+        <v>791</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379734</t>
+          <t xml:space="preserve">311381894</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-12</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 70</t>
+          <t xml:space="preserve">Prins Constantins Vej 3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029712</t>
+          <t xml:space="preserve">100028103</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="J93">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379735</t>
+          <t xml:space="preserve">311384296</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 70</t>
+          <t xml:space="preserve">Ewaldsensvej 3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029712</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J94">
-        <v>126</v>
+        <v>1223</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379735</t>
+          <t xml:space="preserve">311398345</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-09-13</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,40 +7091,40 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 72</t>
+          <t xml:space="preserve">Danasvej 30B</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029711</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379737</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,40 +7166,40 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
+          <t xml:space="preserve">Svend Trøsts Vej 19</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028525</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>791</v>
+        <v>440</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381894</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-12</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,40 +7241,40 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prins Constantins Vej 3</t>
+          <t xml:space="preserve">Fuglevangsvej 8A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028103</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J97">
-        <v>300</v>
+        <v>842</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384296</t>
+          <t xml:space="preserve">311459962</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2030-09-09</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ewaldsensvej 3</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,30 +7326,30 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100030861</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>1223</v>
+        <v>3418</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311398345</t>
+          <t xml:space="preserve">311506322</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-13</t>
+          <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,40 +7391,40 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danasvej 30B</t>
+          <t xml:space="preserve">Filippavej 2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100027259</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>586</v>
+        <v>3232</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311510299</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,40 +7466,40 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svend Trøsts Vej 19</t>
+          <t xml:space="preserve">Filippavej 5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100027255</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>440</v>
+        <v>651</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311511329</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2031-04-10</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,40 +7541,40 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8A</t>
+          <t xml:space="preserve">Frydendalsvej 13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100029030</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>842</v>
+        <v>568</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459866</t>
+          <t xml:space="preserve">311607220</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-09</t>
+          <t xml:space="preserve">2032-06-13</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
+          <t xml:space="preserve">Solbjerg Have 7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,30 +7626,30 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861</t>
+          <t xml:space="preserve">174850</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J102">
-        <v>3418</v>
+        <v>7906</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506322</t>
+          <t xml:space="preserve">311655735</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-24</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,40 +7691,40 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 2</t>
+          <t xml:space="preserve">Solbjerg Have 8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027259</t>
+          <t xml:space="preserve">174851</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J103">
-        <v>3232</v>
+        <v>426</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510299</t>
+          <t xml:space="preserve">311655850</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 5</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027255</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,21 +7785,21 @@
         </is>
       </c>
       <c r="J104">
-        <v>651</v>
+        <v>1016</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511329</t>
+          <t xml:space="preserve">311712714</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-10</t>
+          <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 13</t>
+          <t xml:space="preserve">Sønderjyllands Alle 4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029030</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>568</v>
+        <v>4298</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607220</t>
+          <t xml:space="preserve">311715946</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-13</t>
+          <t xml:space="preserve">2033-10-18</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,40 +7916,40 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 7</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">174850</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>7906</v>
+        <v>474</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655735</t>
+          <t xml:space="preserve">311718502</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,40 +7991,40 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 8</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">174851</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J107">
-        <v>426</v>
+        <v>1407</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655850</t>
+          <t xml:space="preserve">311718497</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Hoffmeyersvej 32</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100029488</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>1016</v>
+        <v>111</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712714</t>
+          <t xml:space="preserve">311718500</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-05</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 4</t>
+          <t xml:space="preserve">Hoffmeyersvej 32</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100029488</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J109">
-        <v>4298</v>
+        <v>1679</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715946</t>
+          <t xml:space="preserve">311718499</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-18</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,17 +8216,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
+          <t xml:space="preserve">Dr. Priemes Vej 3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">1854</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100025651</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>474</v>
+        <v>1434</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718502</t>
+          <t xml:space="preserve">311718872</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>1407</v>
+        <v>5014</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718497</t>
+          <t xml:space="preserve">311718833</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 32</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029488</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>111</v>
+        <v>1518</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718500</t>
+          <t xml:space="preserve">311718915</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,30 +8441,30 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 32</t>
+          <t xml:space="preserve">Amicisvej 11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029488</t>
+          <t xml:space="preserve">100025654</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>1679</v>
+        <v>390</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718499</t>
+          <t xml:space="preserve">311719926</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Priemes Vej 3</t>
+          <t xml:space="preserve">Bülowsvej 34B</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025651</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J114">
-        <v>1434</v>
+        <v>2018</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718872</t>
+          <t xml:space="preserve">311719910</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Godthåbsvej 33</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100026193</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>5014</v>
+        <v>345</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718833</t>
+          <t xml:space="preserve">311719933</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Hollændervej 1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100025653</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>1518</v>
+        <v>298</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718915</t>
+          <t xml:space="preserve">311719925</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 11</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025654</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>390</v>
+        <v>2280</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719926</t>
+          <t xml:space="preserve">311719943</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,30 +8816,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 34B</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J118">
-        <v>2018</v>
+        <v>910</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719910</t>
+          <t xml:space="preserve">311719927</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 33</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026193</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J119">
-        <v>345</v>
+        <v>892</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719933</t>
+          <t xml:space="preserve">311719941</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 1</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025653</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J120">
-        <v>298</v>
+        <v>1827</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719925</t>
+          <t xml:space="preserve">311719948</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Hortensiavej 3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J121">
-        <v>2280</v>
+        <v>575</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719943</t>
+          <t xml:space="preserve">311719924</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Edisonsvej 10</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>910</v>
+        <v>1906</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719927</t>
+          <t xml:space="preserve">311720841</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-08</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Bille Brahes Vej 2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100026838</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>892</v>
+        <v>1898</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719941</t>
+          <t xml:space="preserve">311722042</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Stockflethsvej 4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100029709</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>1827</v>
+        <v>2652</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719948</t>
+          <t xml:space="preserve">311721928</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 3</t>
+          <t xml:space="preserve">Nyelandsvej 23A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>575</v>
+        <v>237</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719924</t>
+          <t xml:space="preserve">311722647</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 10</t>
+          <t xml:space="preserve">Nyelandsvej 23B</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>1906</v>
+        <v>1381</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720841</t>
+          <t xml:space="preserve">311722638</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-08</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bille Brahes Vej 2</t>
+          <t xml:space="preserve">Rolighedsvej 29A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">1958</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026838</t>
+          <t xml:space="preserve">100027933</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>1898</v>
+        <v>809</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722042</t>
+          <t xml:space="preserve">311722651</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 4</t>
+          <t xml:space="preserve">Nyelandsvej 75B</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029709</t>
+          <t xml:space="preserve">100029476</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>2652</v>
+        <v>2174</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721928</t>
+          <t xml:space="preserve">311723087</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23A</t>
+          <t xml:space="preserve">Roskildevej 54</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>237</v>
+        <v>348</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722647</t>
+          <t xml:space="preserve">311723090</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,30 +9716,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23B</t>
+          <t xml:space="preserve">Frederiksberg Alle 63</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1820</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100028276</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>1381</v>
+        <v>130</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722638</t>
+          <t xml:space="preserve">311723249</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-19</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 29A</t>
+          <t xml:space="preserve">Howitzvej 28</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027933</t>
+          <t xml:space="preserve">100027660</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>809</v>
+        <v>6723</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722651</t>
+          <t xml:space="preserve">311723274</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-19</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75B</t>
+          <t xml:space="preserve">Bentzonsvej 49</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029476</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
-        <v>2174</v>
+        <v>941</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723087</t>
+          <t xml:space="preserve">311723412</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54</t>
+          <t xml:space="preserve">Howitzvej 5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100027640</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>348</v>
+        <v>2139</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723090</t>
+          <t xml:space="preserve">311723408</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,40 +10016,40 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Alle 63</t>
+          <t xml:space="preserve">Duevej 51A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028276</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J134">
-        <v>130</v>
+        <v>1142</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723249</t>
+          <t xml:space="preserve">311723677</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-19</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 28</t>
+          <t xml:space="preserve">Lollandsvej 40</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027660</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J135">
-        <v>6723</v>
+        <v>2331</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723274</t>
+          <t xml:space="preserve">311723961</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-19</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bentzonsvej 49</t>
+          <t xml:space="preserve">Troels-Lunds Vej 25</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100029493</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>941</v>
+        <v>4192</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723412</t>
+          <t xml:space="preserve">311723974</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 5</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027640</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J137">
-        <v>2139</v>
+        <v>4063</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723408</t>
+          <t xml:space="preserve">311723983</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,40 +10316,40 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 51A</t>
+          <t xml:space="preserve">Fuglevangsvej 5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>1142</v>
+        <v>2396</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723677</t>
+          <t xml:space="preserve">311723989</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lollandsvej 40</t>
+          <t xml:space="preserve">Fuglevangsvej 8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J139">
-        <v>2331</v>
+        <v>2235</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723961</t>
+          <t xml:space="preserve">311723988</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troels-Lunds Vej 25</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029493</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J140">
-        <v>4192</v>
+        <v>3767</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723974</t>
+          <t xml:space="preserve">311723998</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
+          <t xml:space="preserve">Duevej 53A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J141">
-        <v>4063</v>
+        <v>1859</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723983</t>
+          <t xml:space="preserve">311724465</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 5</t>
+          <t xml:space="preserve">Tesdorpfsvej 19</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100029716</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>2396</v>
+        <v>1897</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723989</t>
+          <t xml:space="preserve">311725944</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>2235</v>
+        <v>7469</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723988</t>
+          <t xml:space="preserve">311726343</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,20 +10776,20 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J144">
-        <v>3767</v>
+        <v>1826</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723998</t>
+          <t xml:space="preserve">311726342</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 53A</t>
+          <t xml:space="preserve">Carl Plougs Vej 4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1913</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J145">
-        <v>1859</v>
+        <v>1283</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724465</t>
+          <t xml:space="preserve">311726476</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 19</t>
+          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029716</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>1897</v>
+        <v>5031</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725944</t>
+          <t xml:space="preserve">311726475</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>7469</v>
+        <v>2221</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726343</t>
+          <t xml:space="preserve">311726873</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Grundtvigsvej 9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1864</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100026309</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>1826</v>
+        <v>10865</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726342</t>
+          <t xml:space="preserve">311727265</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Plougs Vej 4</t>
+          <t xml:space="preserve">La Cours Vej 2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J149">
-        <v>1283</v>
+        <v>5199</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726476</t>
+          <t xml:space="preserve">311727254</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,17 +11216,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
+          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100029769</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>5031</v>
+        <v>1176</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726475</t>
+          <t xml:space="preserve">311733387</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">Pile Alle 33</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">191032, 191033</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J151">
-        <v>2221</v>
+        <v>1248</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726873</t>
+          <t xml:space="preserve">311733392</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,17 +11366,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigsvej 9</t>
+          <t xml:space="preserve">Finsensvej 92</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026309</t>
+          <t xml:space="preserve">100029806</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>10865</v>
+        <v>3370</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727265</t>
+          <t xml:space="preserve">311734724</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-20</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Cours Vej 2</t>
+          <t xml:space="preserve">Frederiksberg Alle 63</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1820</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100028276</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J153">
-        <v>5199</v>
+        <v>146</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727254</t>
+          <t xml:space="preserve">311734449</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
+          <t xml:space="preserve">Falkoner Alle 130</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029769</t>
+          <t xml:space="preserve">100028184</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>1176</v>
+        <v>562</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733387</t>
+          <t xml:space="preserve">311735174</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,30 +11591,30 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 33</t>
+          <t xml:space="preserve">Falkonergårdsvej 21</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">191032, 191033</t>
+          <t xml:space="preserve">100028183</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>1248</v>
+        <v>375</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733392</t>
+          <t xml:space="preserve">311735114</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finsensvej 92</t>
+          <t xml:space="preserve">Sofus Francks Vænge 28</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,20 +11676,20 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029806</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J156">
-        <v>3370</v>
+        <v>856</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734724</t>
+          <t xml:space="preserve">311742694</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-20</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,30 +11741,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Alle 63</t>
+          <t xml:space="preserve">Sofus Francks Vænge 30</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028276</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>146</v>
+        <v>6815</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734449</t>
+          <t xml:space="preserve">311742695</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-22</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Alle 130</t>
+          <t xml:space="preserve">Sofus Francks Vænge 34</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028184</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
-        <v>562</v>
+        <v>706</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735174</t>
+          <t xml:space="preserve">311742696</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkonergårdsvej 21</t>
+          <t xml:space="preserve">Christian Paulsens Vej 26</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028183</t>
+          <t xml:space="preserve">100029283</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>375</v>
+        <v>2340</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735114</t>
+          <t xml:space="preserve">311736719</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 28</t>
+          <t xml:space="preserve">Godthåbsvej 21A</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,20 +11976,20 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>856</v>
+        <v>812</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742694</t>
+          <t xml:space="preserve">311736735</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 30</t>
+          <t xml:space="preserve">Godthåbsvej 21C</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J161">
-        <v>6815</v>
+        <v>241</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742695</t>
+          <t xml:space="preserve">311736736</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 34</t>
+          <t xml:space="preserve">Godthåbsvej 23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>706</v>
+        <v>1290</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742696</t>
+          <t xml:space="preserve">311736733</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 26</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 21</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029283</t>
+          <t xml:space="preserve">100029332</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J163">
-        <v>2340</v>
+        <v>86</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736719</t>
+          <t xml:space="preserve">311736740</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 21A</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029324</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>812</v>
+        <v>2412</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736735</t>
+          <t xml:space="preserve">311736741</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 21C</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029349</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>241</v>
+        <v>2532</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736736</t>
+          <t xml:space="preserve">311737441</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 23</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>1290</v>
+        <v>110</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736733</t>
+          <t xml:space="preserve">311737458</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 21</t>
+          <t xml:space="preserve">Roskildevej 42A</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029332</t>
+          <t xml:space="preserve">100029157</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J167">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736740</t>
+          <t xml:space="preserve">311737456</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
+          <t xml:space="preserve">Stockflethsvej 2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029324</t>
+          <t xml:space="preserve">100029710</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,11 +12585,11 @@
         </is>
       </c>
       <c r="J168">
-        <v>2412</v>
+        <v>60</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736741</t>
+          <t xml:space="preserve">311737445</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
+          <t xml:space="preserve">Nyelandsvej 25B</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029349</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J169">
-        <v>2532</v>
+        <v>467</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737441</t>
+          <t xml:space="preserve">311738410</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J170">
-        <v>110</v>
+        <v>382</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737458</t>
+          <t xml:space="preserve">311738404</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 42A</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029157</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J171">
-        <v>165</v>
+        <v>759</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737456</t>
+          <t xml:space="preserve">311738403</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 2</t>
+          <t xml:space="preserve">Lyøvej 12</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029710</t>
+          <t xml:space="preserve">100025884</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,11 +12885,11 @@
         </is>
       </c>
       <c r="J172">
-        <v>60</v>
+        <v>654</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737445</t>
+          <t xml:space="preserve">311738624</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25B</t>
+          <t xml:space="preserve">Nyelandsvej 25A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12956,15 +12956,15 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J173">
-        <v>467</v>
+        <v>1086</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738410</t>
+          <t xml:space="preserve">311738883</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,20 +13026,20 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>382</v>
+        <v>458</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738404</t>
+          <t xml:space="preserve">311740954</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>759</v>
+        <v>4137</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738403</t>
+          <t xml:space="preserve">311739450</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyøvej 12</t>
+          <t xml:space="preserve">Nyelandsvej 51</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025884</t>
+          <t xml:space="preserve">100025875</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>654</v>
+        <v>541</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738624</t>
+          <t xml:space="preserve">311739362</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25A</t>
+          <t xml:space="preserve">Nyelandsvej 75</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029459</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>1086</v>
+        <v>1009</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738883</t>
+          <t xml:space="preserve">311739367</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-14</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,17 +13316,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Sankt Knuds Vej 32</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100027037</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,11 +13335,11 @@
         </is>
       </c>
       <c r="J178">
-        <v>458</v>
+        <v>846</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740954</t>
+          <t xml:space="preserve">311739928</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J179">
-        <v>4137</v>
+        <v>594</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739450</t>
+          <t xml:space="preserve">311740966</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-26</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 51</t>
+          <t xml:space="preserve">Rosenørns Alle 59</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1970</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025875</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>541</v>
+        <v>1965</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739362</t>
+          <t xml:space="preserve">311741888</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,17 +13541,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75</t>
+          <t xml:space="preserve">Svanholmsvej 15</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1905</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029459</t>
+          <t xml:space="preserve">100027101</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>1009</v>
+        <v>1287</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739367</t>
+          <t xml:space="preserve">311741757</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,17 +13616,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 32</t>
+          <t xml:space="preserve">Vagtelvej 58</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027037</t>
+          <t xml:space="preserve">100027314</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>846</v>
+        <v>1134</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739928</t>
+          <t xml:space="preserve">311741762</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Eversvej 2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100029822</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>594</v>
+        <v>9353</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740966</t>
+          <t xml:space="preserve">311743570</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-26</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,30 +13766,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenørns Alle 59</t>
+          <t xml:space="preserve">Tesdorpfsvej 23</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100029708</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J184">
-        <v>1965</v>
+        <v>291</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741888</t>
+          <t xml:space="preserve">311742345</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanholmsvej 15</t>
+          <t xml:space="preserve">Tesdorpfsvej 25</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027101</t>
+          <t xml:space="preserve">100029707</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>1287</v>
+        <v>1491</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741757</t>
+          <t xml:space="preserve">311742340</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vagtelvej 58</t>
+          <t xml:space="preserve">Nimbusparken 26</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027314</t>
+          <t xml:space="preserve">100029646</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>1134</v>
+        <v>5305</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741762</t>
+          <t xml:space="preserve">311743895</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eversvej 2</t>
+          <t xml:space="preserve">Virginiavej 11</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029822</t>
+          <t xml:space="preserve">100026985</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>9353</v>
+        <v>814</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743570</t>
+          <t xml:space="preserve">311743940</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 23</t>
+          <t xml:space="preserve">Flintholm Alle 25</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029708</t>
+          <t xml:space="preserve">100029803</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>291</v>
+        <v>3250</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742345</t>
+          <t xml:space="preserve">311744589</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 25</t>
+          <t xml:space="preserve">Flintholm Alle 35</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029707</t>
+          <t xml:space="preserve">100029802</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>1491</v>
+        <v>3280</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742340</t>
+          <t xml:space="preserve">311744599</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nimbusparken 26</t>
+          <t xml:space="preserve">Flintholm Alle 45</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029646</t>
+          <t xml:space="preserve">100029790</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>5305</v>
+        <v>2615</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743895</t>
+          <t xml:space="preserve">311744608</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virginiavej 11</t>
+          <t xml:space="preserve">Christian Paulsens Vej 32</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,20 +14301,20 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026985</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J191">
-        <v>814</v>
+        <v>2505</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743940</t>
+          <t xml:space="preserve">311745373</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 25</t>
+          <t xml:space="preserve">Elga Olgas Vej 5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029803</t>
+          <t xml:space="preserve">100029824</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>3250</v>
+        <v>4407</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744589</t>
+          <t xml:space="preserve">311745450</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 35</t>
+          <t xml:space="preserve">Lynge Bygade 60</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3540</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029802</t>
+          <t xml:space="preserve">2252337</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>3280</v>
+        <v>534</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744599</t>
+          <t xml:space="preserve">311745449</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 45</t>
+          <t xml:space="preserve">Sønderjyllands Alle 10</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029790</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>2615</v>
+        <v>3120</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744608</t>
+          <t xml:space="preserve">311767998</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 32</t>
+          <t xml:space="preserve">Nyelandsvej 85</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,30 +14601,30 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">100029472</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>2505</v>
+        <v>4687</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745373</t>
+          <t xml:space="preserve">311746471</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Norca ApS</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elga Olgas Vej 5</t>
+          <t xml:space="preserve">Godthåbsvej 83</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029824</t>
+          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>4407</v>
+        <v>13136</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745450</t>
+          <t xml:space="preserve">311746996</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14736,22 +14736,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynge Bygade 60</t>
+          <t xml:space="preserve">Frederiksvej 51</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252337</t>
+          <t xml:space="preserve">100029085</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="J197">
-        <v>534</v>
+        <v>2080</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745449</t>
+          <t xml:space="preserve">311758493</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 10</t>
+          <t xml:space="preserve">Nordre Fasanvej 81</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">100029721</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>3120</v>
+        <v>787</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767998</t>
+          <t xml:space="preserve">311758487</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 85</t>
+          <t xml:space="preserve">Beringsvej 8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029472</t>
+          <t xml:space="preserve">100030255</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,21 +14910,21 @@
         </is>
       </c>
       <c r="J199">
-        <v>4687</v>
+        <v>413</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746471</t>
+          <t xml:space="preserve">311926722</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-19</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 83</t>
+          <t xml:space="preserve">Hoffmeyersvej 40</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
+          <t xml:space="preserve">100029487</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="J200">
-        <v>13136</v>
+        <v>1071</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746996</t>
+          <t xml:space="preserve">311928517</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-21</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 51</t>
+          <t xml:space="preserve">Nordre Fasanvej 75</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029085</t>
+          <t xml:space="preserve">100029720</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,21 +15060,21 @@
         </is>
       </c>
       <c r="J201">
-        <v>2080</v>
+        <v>1334</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758493</t>
+          <t xml:space="preserve">311928590</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,17 +15116,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 81</t>
+          <t xml:space="preserve">Svanemosegårdsvej 10</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1967</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029721</t>
+          <t xml:space="preserve">100026430</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,21 +15135,21 @@
         </is>
       </c>
       <c r="J202">
-        <v>787</v>
+        <v>446</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758487</t>
+          <t xml:space="preserve">311929077</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">

--- a/public/exports-from-60/11259979.xlsx
+++ b/public/exports-from-60/11259979.xlsx
@@ -2891,17 +2891,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segelckesvej 7</t>
+          <t xml:space="preserve">Thorvaldsensvej 24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030239</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>408</v>
+        <v>3792</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223800</t>
+          <t xml:space="preserve">311223802</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segelckesvej 7</t>
+          <t xml:space="preserve">Storm Petersens Vej 5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,30 +2976,30 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030239</t>
+          <t xml:space="preserve">100047575</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>197</v>
+        <v>297</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223800</t>
+          <t xml:space="preserve">311225730</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-21</t>
+          <t xml:space="preserve">2027-01-31</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 24</t>
+          <t xml:space="preserve">Hortensiavej 11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100025624</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="J41">
-        <v>3792</v>
+        <v>440</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223802</t>
+          <t xml:space="preserve">311226748</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-21</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 5</t>
+          <t xml:space="preserve">Hortensiavej 13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047575</t>
+          <t xml:space="preserve">100025599</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225730</t>
+          <t xml:space="preserve">311226749</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-31</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">230</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 11</t>
+          <t xml:space="preserve">Biskop Svanes Vej 75</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">3460</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025624</t>
+          <t xml:space="preserve">8312706</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="J43">
-        <v>440</v>
+        <v>1322</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226748</t>
+          <t xml:space="preserve">311231330</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3261,22 +3261,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 13</t>
+          <t xml:space="preserve">Nørrevænget 14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025599</t>
+          <t xml:space="preserve">2137707</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,21 +3285,21 @@
         </is>
       </c>
       <c r="J44">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226749</t>
+          <t xml:space="preserve">311227340</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">230</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Svanes Vej 75</t>
+          <t xml:space="preserve">Amicisvej 9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3460</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8312706</t>
+          <t xml:space="preserve">100025655</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="J45">
-        <v>1322</v>
+        <v>340</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231330</t>
+          <t xml:space="preserve">311227832</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 14</t>
+          <t xml:space="preserve">Bülowsvej 14A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137707</t>
+          <t xml:space="preserve">100026669</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="J46">
-        <v>295</v>
+        <v>626</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227340</t>
+          <t xml:space="preserve">311227831</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 9</t>
+          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025655</t>
+          <t xml:space="preserve">100025685</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="J47">
-        <v>340</v>
+        <v>953</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227832</t>
+          <t xml:space="preserve">311229051</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 14A</t>
+          <t xml:space="preserve">Frydendalsvej 19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026669</t>
+          <t xml:space="preserve">100028929</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="J48">
-        <v>626</v>
+        <v>805</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227831</t>
+          <t xml:space="preserve">311229048</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
+          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025685</t>
+          <t xml:space="preserve">100027090</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="J49">
-        <v>953</v>
+        <v>589</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229051</t>
+          <t xml:space="preserve">311230550</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,40 +3716,40 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 19</t>
+          <t xml:space="preserve">Junggreensvej 12B</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028929</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>805</v>
+        <v>1152</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229048</t>
+          <t xml:space="preserve">311230598</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
+          <t xml:space="preserve">N.J. Fjords Alle 15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027090</t>
+          <t xml:space="preserve">100026522</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>589</v>
+        <v>300</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230550</t>
+          <t xml:space="preserve">311230618</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junggreensvej 12B</t>
+          <t xml:space="preserve">N.J. Fjords Alle 17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100026522</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,11 +3885,11 @@
         </is>
       </c>
       <c r="J52">
-        <v>1152</v>
+        <v>376</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230598</t>
+          <t xml:space="preserve">311230618</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 15</t>
+          <t xml:space="preserve">Niels Ebbesens Vej 21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026522</t>
+          <t xml:space="preserve">100027029</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="J53">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230618</t>
+          <t xml:space="preserve">311230611</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 17</t>
+          <t xml:space="preserve">Nyelandsvej 66</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026522</t>
+          <t xml:space="preserve">100029714</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230618</t>
+          <t xml:space="preserve">311230609</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Ebbesens Vej 21</t>
+          <t xml:space="preserve">Sankt Knuds Vej 7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027029</t>
+          <t xml:space="preserve">100026917</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="J55">
-        <v>190</v>
+        <v>433</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230611</t>
+          <t xml:space="preserve">311230540</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,17 +4166,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 66</t>
+          <t xml:space="preserve">Bakkegårds Alle 18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1804</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029714</t>
+          <t xml:space="preserve">191034</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="J56">
-        <v>342</v>
+        <v>1225</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230609</t>
+          <t xml:space="preserve">311230651</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 7</t>
+          <t xml:space="preserve">Dronning Olgas Vej 6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026917</t>
+          <t xml:space="preserve">100028120</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>433</v>
+        <v>580</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230540</t>
+          <t xml:space="preserve">311230652</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,30 +4316,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkegårds Alle 18</t>
+          <t xml:space="preserve">Dronning Olgas Vej 6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">191034</t>
+          <t xml:space="preserve">100028120</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J58">
-        <v>1225</v>
+        <v>72</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230651</t>
+          <t xml:space="preserve">311230652</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Olgas Vej 6</t>
+          <t xml:space="preserve">Rahbeks Alle 19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1801</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028120</t>
+          <t xml:space="preserve">100028743</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>580</v>
+        <v>388</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230652</t>
+          <t xml:space="preserve">311231234</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Olgas Vej 6</t>
+          <t xml:space="preserve">La Cours Vej 2A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028120</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230652</t>
+          <t xml:space="preserve">311231520</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4536,22 +4536,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbeks Alle 19</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028743</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231234</t>
+          <t xml:space="preserve">311231683</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4611,35 +4611,35 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Cours Vej 2A</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J62">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231520</t>
+          <t xml:space="preserve">311231683</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-01</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4686,35 +4686,35 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Thorvaldsensvej 26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J63">
-        <v>1209</v>
+        <v>422</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231683</t>
+          <t xml:space="preserve">311233222</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Oddenvej 90B</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">2428914</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64">
-        <v>144</v>
+        <v>398</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231683</t>
+          <t xml:space="preserve">311233782</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,30 +4841,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 26</t>
+          <t xml:space="preserve">Skellet 27A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J65">
-        <v>422</v>
+        <v>476</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233222</t>
+          <t xml:space="preserve">311233769</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4911,35 +4911,35 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oddenvej 90B</t>
+          <t xml:space="preserve">Skellet 27A</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428914</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J66">
-        <v>398</v>
+        <v>224</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233782</t>
+          <t xml:space="preserve">311233769</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4991,30 +4991,30 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27A</t>
+          <t xml:space="preserve">Vodroffsvej 44</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100027252</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>476</v>
+        <v>178</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233769</t>
+          <t xml:space="preserve">311234441</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,30 +5066,30 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27A</t>
+          <t xml:space="preserve">Vodroffsvej 46</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100027252</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>224</v>
+        <v>1486</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233769</t>
+          <t xml:space="preserve">311234441</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,30 +5141,30 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vodroffsvej 44</t>
+          <t xml:space="preserve">Allegade 31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027252</t>
+          <t xml:space="preserve">100025702</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>178</v>
+        <v>29942</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234441</t>
+          <t xml:space="preserve">311234962</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vodroffsvej 46</t>
+          <t xml:space="preserve">Skellet 27C</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027252</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>1486</v>
+        <v>1915</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234441</t>
+          <t xml:space="preserve">311236260</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 31</t>
+          <t xml:space="preserve">Edisonsvej 3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025702</t>
+          <t xml:space="preserve">100025577</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>29942</v>
+        <v>228</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234962</t>
+          <t xml:space="preserve">311247695</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,30 +5366,30 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27C</t>
+          <t xml:space="preserve">Edisonsvej 3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100025577</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>1915</v>
+        <v>525</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236260</t>
+          <t xml:space="preserve">311247695</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 3</t>
+          <t xml:space="preserve">Ingemannsvej 21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1964</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025577</t>
+          <t xml:space="preserve">100026391</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>228</v>
+        <v>1000</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247695</t>
+          <t xml:space="preserve">311248626</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,40 +5516,40 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 3</t>
+          <t xml:space="preserve">Søndre Fasanvej 40</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025577</t>
+          <t xml:space="preserve">100028380</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>525</v>
+        <v>1699</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247695</t>
+          <t xml:space="preserve">311248632</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingemannsvej 21</t>
+          <t xml:space="preserve">Bülowsvej 20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1964</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026391</t>
+          <t xml:space="preserve">100026777</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>1000</v>
+        <v>454</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248626</t>
+          <t xml:space="preserve">311248790</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Fasanvej 40</t>
+          <t xml:space="preserve">Storm Petersens Vej 4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028380</t>
+          <t xml:space="preserve">100047577</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="J76">
-        <v>1699</v>
+        <v>2679</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248632</t>
+          <t xml:space="preserve">311256544</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,40 +5741,40 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 20</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026777</t>
+          <t xml:space="preserve">100030861, 100227750, 100227751</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J77">
-        <v>454</v>
+        <v>6331</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248790</t>
+          <t xml:space="preserve">311268443</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-08-24</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 4</t>
+          <t xml:space="preserve">Mariendalsvej 21A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047577</t>
+          <t xml:space="preserve">100028065</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>2679</v>
+        <v>1008</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256544</t>
+          <t xml:space="preserve">311269303</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,40 +5891,40 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861, 100227750, 100227751</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>6331</v>
+        <v>825</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268443</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-24</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,40 +5966,40 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariendalsvej 21A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028065</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>1008</v>
+        <v>439</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269303</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-29</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6056,15 +6056,15 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J81">
-        <v>825</v>
+        <v>464</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311285951</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J82">
-        <v>439</v>
+        <v>371</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,40 +6191,40 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Dirch Passers Allé 8A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029781</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>464</v>
+        <v>3880</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285951</t>
+          <t xml:space="preserve">311293188</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,40 +6266,40 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Helgesvej 29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100026188</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>371</v>
+        <v>6682</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311373826</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-04-30</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirch Passers Allé 8A</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029781</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,21 +6360,21 @@
         </is>
       </c>
       <c r="J85">
-        <v>3880</v>
+        <v>386</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293188</t>
+          <t xml:space="preserve">311379731</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 29</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,20 +6426,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026188</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>6682</v>
+        <v>443</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373826</t>
+          <t xml:space="preserve">311379734</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-30</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Nyelandsvej 70</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100029712</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,11 +6510,11 @@
         </is>
       </c>
       <c r="J87">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379731</t>
+          <t xml:space="preserve">311379735</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Nyelandsvej 70</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100029712</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J88">
-        <v>443</v>
+        <v>126</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379734</t>
+          <t xml:space="preserve">311379735</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 70</t>
+          <t xml:space="preserve">Nyelandsvej 72</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029712</t>
+          <t xml:space="preserve">100029711</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,11 +6660,11 @@
         </is>
       </c>
       <c r="J89">
-        <v>311</v>
+        <v>542</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379735</t>
+          <t xml:space="preserve">311379737</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 70</t>
+          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029712</t>
+          <t xml:space="preserve">100028525</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>126</v>
+        <v>791</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379735</t>
+          <t xml:space="preserve">311381894</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-12</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 72</t>
+          <t xml:space="preserve">Prins Constantins Vej 3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029711</t>
+          <t xml:space="preserve">100028103</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>542</v>
+        <v>300</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379737</t>
+          <t xml:space="preserve">311384296</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
+          <t xml:space="preserve">Ewaldsensvej 3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028525</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J92">
-        <v>791</v>
+        <v>1223</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381894</t>
+          <t xml:space="preserve">311398345</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-12</t>
+          <t xml:space="preserve">2029-09-13</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,40 +6941,40 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prins Constantins Vej 3</t>
+          <t xml:space="preserve">Danasvej 30B</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028103</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J93">
-        <v>300</v>
+        <v>586</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384296</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,40 +7016,40 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ewaldsensvej 3</t>
+          <t xml:space="preserve">Svend Trøsts Vej 19</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
-        <v>1223</v>
+        <v>440</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311398345</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-13</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,40 +7091,40 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danasvej 30B</t>
+          <t xml:space="preserve">Fuglevangsvej 8A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J95">
-        <v>586</v>
+        <v>842</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311459962</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2030-09-09</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,40 +7166,40 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svend Trøsts Vej 19</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100030861</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>440</v>
+        <v>3418</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311506322</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,40 +7241,40 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8A</t>
+          <t xml:space="preserve">Filippavej 2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100027259</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>842</v>
+        <v>3232</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459962</t>
+          <t xml:space="preserve">311510299</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-09</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
+          <t xml:space="preserve">Filippavej 5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861</t>
+          <t xml:space="preserve">100027255</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>3418</v>
+        <v>651</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506322</t>
+          <t xml:space="preserve">311511329</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-24</t>
+          <t xml:space="preserve">2031-04-10</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,17 +7391,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 2</t>
+          <t xml:space="preserve">Frydendalsvej 13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027259</t>
+          <t xml:space="preserve">100029030</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="J99">
-        <v>3232</v>
+        <v>568</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510299</t>
+          <t xml:space="preserve">311607220</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2032-06-13</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,40 +7466,40 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 5</t>
+          <t xml:space="preserve">Solbjerg Have 7</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027255</t>
+          <t xml:space="preserve">174850</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J100">
-        <v>651</v>
+        <v>7906</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511329</t>
+          <t xml:space="preserve">311655735</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-10</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,40 +7541,40 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 13</t>
+          <t xml:space="preserve">Solbjerg Have 8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029030</t>
+          <t xml:space="preserve">174851</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J101">
-        <v>568</v>
+        <v>426</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607220</t>
+          <t xml:space="preserve">311655850</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-13</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 7</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,30 +7626,30 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">174850</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>7906</v>
+        <v>1016</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655735</t>
+          <t xml:space="preserve">311712714</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 8</t>
+          <t xml:space="preserve">Sønderjyllands Alle 4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,30 +7701,30 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">174851</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>426</v>
+        <v>4298</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655850</t>
+          <t xml:space="preserve">311715946</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-18</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>1016</v>
+        <v>474</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712714</t>
+          <t xml:space="preserve">311718502</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-05</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 4</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J105">
-        <v>4298</v>
+        <v>1407</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715946</t>
+          <t xml:space="preserve">311718497</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-18</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
+          <t xml:space="preserve">Hoffmeyersvej 32</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100029488</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J106">
-        <v>474</v>
+        <v>111</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718502</t>
+          <t xml:space="preserve">311718500</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,30 +7991,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
+          <t xml:space="preserve">Hoffmeyersvej 32</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100029488</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J107">
-        <v>1407</v>
+        <v>1679</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718497</t>
+          <t xml:space="preserve">311718499</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 32</t>
+          <t xml:space="preserve">Dr. Priemes Vej 3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1854</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029488</t>
+          <t xml:space="preserve">100025651</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>111</v>
+        <v>1434</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718500</t>
+          <t xml:space="preserve">311718872</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 32</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029488</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>1679</v>
+        <v>5014</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718499</t>
+          <t xml:space="preserve">311718833</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,30 +8216,30 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Priemes Vej 3</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025651</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J110">
-        <v>1434</v>
+        <v>1518</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718872</t>
+          <t xml:space="preserve">311718915</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Amicisvej 11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100025654</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>5014</v>
+        <v>390</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718833</t>
+          <t xml:space="preserve">311719926</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Bülowsvej 34B</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J112">
-        <v>1518</v>
+        <v>2018</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718915</t>
+          <t xml:space="preserve">311719910</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 11</t>
+          <t xml:space="preserve">Godthåbsvej 33</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025654</t>
+          <t xml:space="preserve">100026193</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719926</t>
+          <t xml:space="preserve">311719933</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 34B</t>
+          <t xml:space="preserve">Hollændervej 1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100025653</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>2018</v>
+        <v>298</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719910</t>
+          <t xml:space="preserve">311719925</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 33</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026193</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>345</v>
+        <v>2280</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719933</t>
+          <t xml:space="preserve">311719943</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 1</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025653</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J116">
-        <v>298</v>
+        <v>910</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719925</t>
+          <t xml:space="preserve">311719927</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8756,15 +8756,15 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J117">
-        <v>2280</v>
+        <v>892</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719943</t>
+          <t xml:space="preserve">311719941</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8831,15 +8831,15 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J118">
-        <v>910</v>
+        <v>1827</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719927</t>
+          <t xml:space="preserve">311719948</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Hortensiavej 3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>892</v>
+        <v>575</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719941</t>
+          <t xml:space="preserve">311719924</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Edisonsvej 10</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>1827</v>
+        <v>1906</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719948</t>
+          <t xml:space="preserve">311720841</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-08</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 3</t>
+          <t xml:space="preserve">Bille Brahes Vej 2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100026838</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>575</v>
+        <v>1898</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719924</t>
+          <t xml:space="preserve">311722042</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 10</t>
+          <t xml:space="preserve">Stockflethsvej 4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100029709</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>1906</v>
+        <v>2652</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720841</t>
+          <t xml:space="preserve">311721928</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-08</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bille Brahes Vej 2</t>
+          <t xml:space="preserve">Nyelandsvej 23A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026838</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J123">
-        <v>1898</v>
+        <v>237</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722042</t>
+          <t xml:space="preserve">311722647</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 4</t>
+          <t xml:space="preserve">Nyelandsvej 23B</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,20 +9276,20 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029709</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>2652</v>
+        <v>1381</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721928</t>
+          <t xml:space="preserve">311722638</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,30 +9341,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23A</t>
+          <t xml:space="preserve">Rolighedsvej 29A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1958</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100027933</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>237</v>
+        <v>809</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722647</t>
+          <t xml:space="preserve">311722651</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23B</t>
+          <t xml:space="preserve">Nyelandsvej 75B</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029476</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>1381</v>
+        <v>2174</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722638</t>
+          <t xml:space="preserve">311723087</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 29A</t>
+          <t xml:space="preserve">Roskildevej 54</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027933</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J127">
-        <v>809</v>
+        <v>348</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722651</t>
+          <t xml:space="preserve">311723090</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75B</t>
+          <t xml:space="preserve">Frederiksberg Alle 63</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1820</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029476</t>
+          <t xml:space="preserve">100028276</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>2174</v>
+        <v>130</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723087</t>
+          <t xml:space="preserve">311723249</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-19</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54</t>
+          <t xml:space="preserve">Howitzvej 28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,20 +9651,20 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100027660</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>348</v>
+        <v>6723</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723090</t>
+          <t xml:space="preserve">311723274</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-19</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,30 +9716,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Alle 63</t>
+          <t xml:space="preserve">Bentzonsvej 49</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028276</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>130</v>
+        <v>941</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723249</t>
+          <t xml:space="preserve">311723412</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-19</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 28</t>
+          <t xml:space="preserve">Howitzvej 5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027660</t>
+          <t xml:space="preserve">100027640</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>6723</v>
+        <v>2139</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723274</t>
+          <t xml:space="preserve">311723408</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-19</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bentzonsvej 49</t>
+          <t xml:space="preserve">Duevej 51A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,30 +9876,30 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J132">
-        <v>941</v>
+        <v>1142</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723412</t>
+          <t xml:space="preserve">311723677</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 5</t>
+          <t xml:space="preserve">Lollandsvej 40</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027640</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>2139</v>
+        <v>2331</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723408</t>
+          <t xml:space="preserve">311723961</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 51A</t>
+          <t xml:space="preserve">Troels-Lunds Vej 25</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,25 +10026,25 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100029493</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>1142</v>
+        <v>4192</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723677</t>
+          <t xml:space="preserve">311723974</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lollandsvej 40</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J135">
-        <v>2331</v>
+        <v>4063</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723961</t>
+          <t xml:space="preserve">311723983</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troels-Lunds Vej 25</t>
+          <t xml:space="preserve">Fuglevangsvej 5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029493</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>4192</v>
+        <v>2396</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723974</t>
+          <t xml:space="preserve">311723989</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,30 +10241,30 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
+          <t xml:space="preserve">Fuglevangsvej 8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J137">
-        <v>4063</v>
+        <v>2235</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723983</t>
+          <t xml:space="preserve">311723988</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,30 +10316,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 5</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J138">
-        <v>2396</v>
+        <v>3767</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723989</t>
+          <t xml:space="preserve">311723998</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8</t>
+          <t xml:space="preserve">Duevej 53A</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J139">
-        <v>2235</v>
+        <v>1859</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723988</t>
+          <t xml:space="preserve">311724465</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">Tesdorpfsvej 19</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029716</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>3767</v>
+        <v>1897</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723998</t>
+          <t xml:space="preserve">311725944</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 53A</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>1859</v>
+        <v>7469</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724465</t>
+          <t xml:space="preserve">311726343</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 19</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029716</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J142">
-        <v>1897</v>
+        <v>1826</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725944</t>
+          <t xml:space="preserve">311726342</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Carl Plougs Vej 4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1913</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J143">
-        <v>7469</v>
+        <v>1283</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726343</t>
+          <t xml:space="preserve">311726476</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>1826</v>
+        <v>5031</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726342</t>
+          <t xml:space="preserve">311726475</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Plougs Vej 4</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>1283</v>
+        <v>2221</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726476</t>
+          <t xml:space="preserve">311726873</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
+          <t xml:space="preserve">Grundtvigsvej 9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">1864</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100026309</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>5031</v>
+        <v>10865</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726475</t>
+          <t xml:space="preserve">311727265</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">La Cours Vej 2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>2221</v>
+        <v>5199</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726873</t>
+          <t xml:space="preserve">311727254</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigsvej 9</t>
+          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026309</t>
+          <t xml:space="preserve">100029769</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>10865</v>
+        <v>1176</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727265</t>
+          <t xml:space="preserve">311733387</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Cours Vej 2</t>
+          <t xml:space="preserve">Pile Alle 33</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,20 +11151,20 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">191032, 191033</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>5199</v>
+        <v>1248</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727254</t>
+          <t xml:space="preserve">311733392</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
+          <t xml:space="preserve">Finsensvej 92</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029769</t>
+          <t xml:space="preserve">100029806</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>1176</v>
+        <v>3370</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733387</t>
+          <t xml:space="preserve">311734724</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-01-20</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 33</t>
+          <t xml:space="preserve">Frederiksberg Alle 63</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1820</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">191032, 191033</t>
+          <t xml:space="preserve">100028276</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J151">
-        <v>1248</v>
+        <v>146</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733392</t>
+          <t xml:space="preserve">311734449</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-01-22</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finsensvej 92</t>
+          <t xml:space="preserve">Falkoner Alle 130</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029806</t>
+          <t xml:space="preserve">100028184</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>3370</v>
+        <v>562</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734724</t>
+          <t xml:space="preserve">311735174</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-20</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Alle 63</t>
+          <t xml:space="preserve">Falkonergårdsvej 21</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028276</t>
+          <t xml:space="preserve">100028183</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>146</v>
+        <v>375</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734449</t>
+          <t xml:space="preserve">311735114</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-22</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Alle 130</t>
+          <t xml:space="preserve">Sofus Francks Vænge 28</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028184</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>562</v>
+        <v>856</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735174</t>
+          <t xml:space="preserve">311742694</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,30 +11591,30 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkonergårdsvej 21</t>
+          <t xml:space="preserve">Sofus Francks Vænge 30</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028183</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>375</v>
+        <v>6815</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735114</t>
+          <t xml:space="preserve">311742695</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 28</t>
+          <t xml:space="preserve">Sofus Francks Vænge 34</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,15 +11681,15 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J156">
-        <v>856</v>
+        <v>706</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742694</t>
+          <t xml:space="preserve">311742696</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 30</t>
+          <t xml:space="preserve">Christian Paulsens Vej 26</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100029283</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>6815</v>
+        <v>2340</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742695</t>
+          <t xml:space="preserve">311736719</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 34</t>
+          <t xml:space="preserve">Godthåbsvej 21A</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>706</v>
+        <v>812</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742696</t>
+          <t xml:space="preserve">311736735</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 26</t>
+          <t xml:space="preserve">Godthåbsvej 21C</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029283</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J159">
-        <v>2340</v>
+        <v>241</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736719</t>
+          <t xml:space="preserve">311736736</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 21A</t>
+          <t xml:space="preserve">Godthåbsvej 23</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>812</v>
+        <v>1290</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736735</t>
+          <t xml:space="preserve">311736733</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 21C</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 21</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029332</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J161">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736736</t>
+          <t xml:space="preserve">311736740</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 23</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029324</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>1290</v>
+        <v>2412</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736733</t>
+          <t xml:space="preserve">311736741</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 21</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029332</t>
+          <t xml:space="preserve">100029349</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>86</v>
+        <v>2532</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736740</t>
+          <t xml:space="preserve">311737441</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029324</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J164">
-        <v>2412</v>
+        <v>110</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736741</t>
+          <t xml:space="preserve">311737458</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
+          <t xml:space="preserve">Roskildevej 42A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029349</t>
+          <t xml:space="preserve">100029157</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>2532</v>
+        <v>165</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737441</t>
+          <t xml:space="preserve">311737456</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Stockflethsvej 2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100029710</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737458</t>
+          <t xml:space="preserve">311737445</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 42A</t>
+          <t xml:space="preserve">Nyelandsvej 25B</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029157</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J167">
-        <v>165</v>
+        <v>467</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737456</t>
+          <t xml:space="preserve">311738410</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 2</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029710</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J168">
-        <v>60</v>
+        <v>382</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737445</t>
+          <t xml:space="preserve">311738404</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25B</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J169">
-        <v>467</v>
+        <v>759</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738410</t>
+          <t xml:space="preserve">311738403</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Lyøvej 12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100025884</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>382</v>
+        <v>654</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738404</t>
+          <t xml:space="preserve">311738624</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Nyelandsvej 25A</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J171">
-        <v>759</v>
+        <v>1086</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738403</t>
+          <t xml:space="preserve">311738883</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyøvej 12</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025884</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,11 +12885,11 @@
         </is>
       </c>
       <c r="J172">
-        <v>654</v>
+        <v>458</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738624</t>
+          <t xml:space="preserve">311740954</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25A</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J173">
-        <v>1086</v>
+        <v>4137</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738883</t>
+          <t xml:space="preserve">311739450</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-14</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Nyelandsvej 51</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100025875</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>458</v>
+        <v>541</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740954</t>
+          <t xml:space="preserve">311739362</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Nyelandsvej 75</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100029459</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>4137</v>
+        <v>1009</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739450</t>
+          <t xml:space="preserve">311739367</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 51</t>
+          <t xml:space="preserve">Sankt Knuds Vej 32</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025875</t>
+          <t xml:space="preserve">100027037</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>541</v>
+        <v>846</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739362</t>
+          <t xml:space="preserve">311739928</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029459</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J177">
-        <v>1009</v>
+        <v>594</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739367</t>
+          <t xml:space="preserve">311740966</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-26</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 32</t>
+          <t xml:space="preserve">Rosenørns Alle 59</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1970</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027037</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J178">
-        <v>846</v>
+        <v>1965</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739928</t>
+          <t xml:space="preserve">311741888</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Svanholmsvej 15</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1905</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100027101</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>594</v>
+        <v>1287</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740966</t>
+          <t xml:space="preserve">311741757</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-26</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenørns Alle 59</t>
+          <t xml:space="preserve">Vagtelvej 58</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100027314</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>1965</v>
+        <v>1134</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741888</t>
+          <t xml:space="preserve">311741762</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,17 +13541,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanholmsvej 15</t>
+          <t xml:space="preserve">Eversvej 2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027101</t>
+          <t xml:space="preserve">100029822</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>1287</v>
+        <v>9353</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741757</t>
+          <t xml:space="preserve">311743570</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vagtelvej 58</t>
+          <t xml:space="preserve">Tesdorpfsvej 23</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027314</t>
+          <t xml:space="preserve">100029708</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>1134</v>
+        <v>291</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741762</t>
+          <t xml:space="preserve">311742345</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eversvej 2</t>
+          <t xml:space="preserve">Tesdorpfsvej 25</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029822</t>
+          <t xml:space="preserve">100029707</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>9353</v>
+        <v>1491</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743570</t>
+          <t xml:space="preserve">311742340</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 23</t>
+          <t xml:space="preserve">Nimbusparken 26</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029708</t>
+          <t xml:space="preserve">100029646</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>291</v>
+        <v>5305</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742345</t>
+          <t xml:space="preserve">311743895</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 25</t>
+          <t xml:space="preserve">Virginiavej 11</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029707</t>
+          <t xml:space="preserve">100026985</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>1491</v>
+        <v>814</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742340</t>
+          <t xml:space="preserve">311743940</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nimbusparken 26</t>
+          <t xml:space="preserve">Flintholm Alle 25</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029646</t>
+          <t xml:space="preserve">100029803</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>5305</v>
+        <v>3250</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743895</t>
+          <t xml:space="preserve">311744589</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virginiavej 11</t>
+          <t xml:space="preserve">Flintholm Alle 35</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026985</t>
+          <t xml:space="preserve">100029802</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>814</v>
+        <v>3280</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743940</t>
+          <t xml:space="preserve">311744599</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 25</t>
+          <t xml:space="preserve">Flintholm Alle 45</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029803</t>
+          <t xml:space="preserve">100029790</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>3250</v>
+        <v>2615</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744589</t>
+          <t xml:space="preserve">311744608</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 35</t>
+          <t xml:space="preserve">Christian Paulsens Vej 32</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029802</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J189">
-        <v>3280</v>
+        <v>2505</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744599</t>
+          <t xml:space="preserve">311745373</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 45</t>
+          <t xml:space="preserve">Elga Olgas Vej 5</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029790</t>
+          <t xml:space="preserve">100029824</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>2615</v>
+        <v>4407</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744608</t>
+          <t xml:space="preserve">311745450</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14286,35 +14286,35 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 32</t>
+          <t xml:space="preserve">Lynge Bygade 60</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3540</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">2252337</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>2505</v>
+        <v>534</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745373</t>
+          <t xml:space="preserve">311745449</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elga Olgas Vej 5</t>
+          <t xml:space="preserve">Sønderjyllands Alle 10</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029824</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>4407</v>
+        <v>3120</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745450</t>
+          <t xml:space="preserve">311767998</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynge Bygade 60</t>
+          <t xml:space="preserve">Nyelandsvej 85</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252337</t>
+          <t xml:space="preserve">100029472</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,21 +14460,21 @@
         </is>
       </c>
       <c r="J193">
-        <v>534</v>
+        <v>4687</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745449</t>
+          <t xml:space="preserve">311746471</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Norca ApS</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 10</t>
+          <t xml:space="preserve">Godthåbsvej 83</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>3120</v>
+        <v>13136</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767998</t>
+          <t xml:space="preserve">311746996</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 85</t>
+          <t xml:space="preserve">Frederiksvej 51</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029472</t>
+          <t xml:space="preserve">100029085</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,21 +14610,21 @@
         </is>
       </c>
       <c r="J195">
-        <v>4687</v>
+        <v>2080</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746471</t>
+          <t xml:space="preserve">311758493</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-19</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 83</t>
+          <t xml:space="preserve">Nordre Fasanvej 81</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
+          <t xml:space="preserve">100029721</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>13136</v>
+        <v>787</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746996</t>
+          <t xml:space="preserve">311758487</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-21</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 51</t>
+          <t xml:space="preserve">Beringsvej 8</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029085</t>
+          <t xml:space="preserve">100030255</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14760,21 +14760,21 @@
         </is>
       </c>
       <c r="J197">
-        <v>2080</v>
+        <v>413</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758493</t>
+          <t xml:space="preserve">311926722</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 81</t>
+          <t xml:space="preserve">Hoffmeyersvej 40</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029721</t>
+          <t xml:space="preserve">100029487</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,21 +14835,21 @@
         </is>
       </c>
       <c r="J198">
-        <v>787</v>
+        <v>1071</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758487</t>
+          <t xml:space="preserve">311928517</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beringsvej 8</t>
+          <t xml:space="preserve">Nordre Fasanvej 75</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030255</t>
+          <t xml:space="preserve">100029720</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>413</v>
+        <v>1334</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926722</t>
+          <t xml:space="preserve">311928590</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-18</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 40</t>
+          <t xml:space="preserve">Svanemosegårdsvej 10</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1967</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029487</t>
+          <t xml:space="preserve">100026430</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>1071</v>
+        <v>446</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928517</t>
+          <t xml:space="preserve">311929077</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 75</t>
+          <t xml:space="preserve">Segelckesvej 7</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029720</t>
+          <t xml:space="preserve">100030239</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,11 +15060,11 @@
         </is>
       </c>
       <c r="J201">
-        <v>1334</v>
+        <v>408</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928590</t>
+          <t xml:space="preserve">311930766</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,30 +15116,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosegårdsvej 10</t>
+          <t xml:space="preserve">Segelckesvej 7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1967</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026430</t>
+          <t xml:space="preserve">100030239</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J202">
-        <v>446</v>
+        <v>197</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929077</t>
+          <t xml:space="preserve">311930765</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
